--- a/data/trans_orig/P79_n_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P79_n_R2-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16652</t>
+          <t>18356</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>8841</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32972</t>
+          <t>36557</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>24480</t>
+          <t>24807</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13340</t>
+          <t>13405</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42365</t>
+          <t>41103</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>41131</t>
+          <t>43163</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24320</t>
+          <t>26596</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62755</t>
+          <t>65337</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>383335</t>
+          <t>389437</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>367015</t>
+          <t>371236</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>393001</t>
+          <t>398952</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>288720</t>
+          <t>337705</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270835</t>
+          <t>321409</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>299860</t>
+          <t>349107</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>672056</t>
+          <t>727142</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>650432</t>
+          <t>704968</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>688867</t>
+          <t>743709</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14583</t>
+          <t>17104</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24742</t>
+          <t>29345</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12912</t>
+          <t>15991</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>9374</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21524</t>
+          <t>25793</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>27494</t>
+          <t>33096</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17413</t>
+          <t>21639</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39308</t>
+          <t>46577</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>408964</t>
+          <t>459786</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>398805</t>
+          <t>447545</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>415727</t>
+          <t>467421</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>499181</t>
+          <t>485742</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>490569</t>
+          <t>475940</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>505576</t>
+          <t>492359</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>908146</t>
+          <t>945527</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>896332</t>
+          <t>932046</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>918227</t>
+          <t>956984</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>24626</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10559</t>
+          <t>16299</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28141</t>
+          <t>37192</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21101</t>
+          <t>26863</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14155</t>
+          <t>19131</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30228</t>
+          <t>36444</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>39253</t>
+          <t>51489</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28702</t>
+          <t>39506</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51758</t>
+          <t>66240</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>518186</t>
+          <t>596211</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>508197</t>
+          <t>583645</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>525779</t>
+          <t>604538</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>570901</t>
+          <t>596330</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>561774</t>
+          <t>586749</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>577847</t>
+          <t>604062</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1089087</t>
+          <t>1192540</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1076582</t>
+          <t>1177789</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1099638</t>
+          <t>1204523</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26925</t>
+          <t>29727</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10874</t>
+          <t>19668</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43884</t>
+          <t>42374</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25306</t>
+          <t>30332</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18100</t>
+          <t>22106</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33847</t>
+          <t>40272</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>52230</t>
+          <t>60059</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31987</t>
+          <t>46700</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71498</t>
+          <t>74290</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>860861</t>
+          <t>670890</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>843902</t>
+          <t>658243</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>876912</t>
+          <t>680949</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>687575</t>
+          <t>706554</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>679034</t>
+          <t>696614</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>694781</t>
+          <t>714780</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1548437</t>
+          <t>1377445</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1529169</t>
+          <t>1363214</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1568680</t>
+          <t>1390804</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>26943</t>
+          <t>31187</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19322</t>
+          <t>22502</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38342</t>
+          <t>43875</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19450</t>
+          <t>23083</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14099</t>
+          <t>16585</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27264</t>
+          <t>32792</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>46394</t>
+          <t>54270</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35365</t>
+          <t>42965</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60158</t>
+          <t>69314</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>534291</t>
+          <t>578159</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>522892</t>
+          <t>565471</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>541912</t>
+          <t>586844</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>528455</t>
+          <t>585772</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>520641</t>
+          <t>576063</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>533806</t>
+          <t>592270</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1062745</t>
+          <t>1163932</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1048981</t>
+          <t>1148888</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1073774</t>
+          <t>1175237</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12664</t>
+          <t>14445</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19173</t>
+          <t>21716</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14883</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>11092</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26702</t>
+          <t>22956</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>27547</t>
+          <t>30918</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12913</t>
+          <t>22746</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>40869</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>355501</t>
+          <t>392635</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>348992</t>
+          <t>385364</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>360230</t>
+          <t>397917</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>593485</t>
+          <t>422692</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>581666</t>
+          <t>416210</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>601910</t>
+          <t>428074</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>948986</t>
+          <t>815328</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>937946</t>
+          <t>805377</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>963620</t>
+          <t>823500</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16247</t>
+          <t>17952</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,22 +2818,22 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>12213</t>
+          <t>13643</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17733</t>
+          <t>19988</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>22390</t>
+          <t>24882</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16539</t>
+          <t>18147</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30573</t>
+          <t>33703</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>272582</t>
+          <t>298959</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>266512</t>
+          <t>292246</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>276678</t>
+          <t>303770</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,27 +2931,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>413618</t>
+          <t>450966</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>408098</t>
+          <t>444621</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>418045</t>
+          <t>456112</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>686200</t>
+          <t>749925</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>678017</t>
+          <t>741104</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>692051</t>
+          <t>756660</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,102 +3126,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>126095</t>
+          <t>146683</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>98439</t>
+          <t>122482</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>156452</t>
+          <t>177615</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>151194</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>130758</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>176427</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>4,05%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>297877</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>264928</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>335361</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>3,64%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>130345</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>102614</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>155967</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>256440</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>217030</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>298878</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -3239,102 +3239,102 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3333722</t>
+          <t>3386079</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3303365</t>
+          <t>3355147</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3361378</t>
+          <t>3410280</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>95,85%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>94,97%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>5177</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>3585760</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>3560527</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3606196</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>95,95%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>95,28%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>96,5%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>8416</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>6971839</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>6934355</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>7004788</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>95,9%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>95,39%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>96,36%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>95,48%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>97,15%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>5177</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3581935</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>3556313</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3609666</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>95,8%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>97,24%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>8416</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>6915657</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>6873219</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6955067</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>96,42%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>95,83%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
